--- a/output/pdf_financials_xlsx/TMED.xlsx
+++ b/output/pdf_financials_xlsx/TMED.xlsx
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.011503</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.009794000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.013794</v>
       </c>
     </row>
     <row r="35">
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.000217</v>
+        <v>0.01172</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.000217</v>
+        <v>0.010011</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.000217</v>
+        <v>0.014011</v>
       </c>
     </row>
     <row r="37">
@@ -1346,13 +1346,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.020668</v>
+        <v>0.009165</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.010114</v>
+        <v>0.00032</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.019119</v>
+        <v>0.005325</v>
       </c>
     </row>
     <row r="49">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">

--- a/output/pdf_financials_xlsx/TMED.xlsx
+++ b/output/pdf_financials_xlsx/TMED.xlsx
@@ -480,20 +480,14 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -502,20 +496,14 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -524,20 +512,14 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -546,20 +528,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.193809</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.194862</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.229688</v>
       </c>
     </row>
     <row r="8">
@@ -568,20 +544,14 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -590,20 +560,14 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -612,20 +576,14 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.193809</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.194862</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.229688</v>
       </c>
     </row>
     <row r="11">
@@ -634,20 +592,14 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.606112</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.297243</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.340158</v>
       </c>
     </row>
     <row r="12">
@@ -656,20 +608,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -678,20 +624,14 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -700,20 +640,14 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -722,20 +656,14 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>-0.013275</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-0.015911</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.00263</v>
       </c>
     </row>
     <row r="16">
@@ -744,20 +672,14 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.643475</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.296259</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-4.061553</v>
       </c>
     </row>
     <row r="17">
@@ -766,20 +688,14 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.832062</v>
       </c>
     </row>
     <row r="18">
@@ -832,20 +748,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.643475</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.296259</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-3.229491</v>
       </c>
     </row>
     <row r="21">
@@ -854,20 +764,14 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -876,20 +780,14 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0.020473</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0.027006</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.02333</v>
       </c>
     </row>
     <row r="23">
@@ -898,10 +796,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.643475</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.296259</v>
@@ -921,15 +817,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="25">
@@ -943,15 +835,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="26">
@@ -965,15 +853,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>14.81295</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>11.533896</v>
       </c>
     </row>
     <row r="27">
@@ -982,20 +866,14 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.643475</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.296259</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-4.061553</v>
       </c>
     </row>
     <row r="28">
@@ -1004,20 +882,14 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1026,20 +898,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.643475</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.296259</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-4.061553</v>
       </c>
     </row>
     <row r="30">
@@ -1070,20 +936,14 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-20.48630166835198</v>
       </c>
     </row>
     <row r="32">
@@ -2170,10 +2030,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.643475</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.296259</v>
@@ -2188,10 +2046,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -2206,10 +2062,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.015193</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.031268</v>
@@ -2224,10 +2078,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -2242,10 +2094,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.003345</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0.008845</v>
@@ -2260,10 +2110,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.03828</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.090449</v>
@@ -2278,10 +2126,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -2296,10 +2142,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.019742</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.068026</v>
@@ -2314,10 +2158,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -2332,10 +2174,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -2350,10 +2190,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -2368,10 +2206,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -2386,10 +2222,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2404,10 +2238,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -2422,10 +2254,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -2440,10 +2270,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -2458,10 +2286,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -2476,10 +2302,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -2494,10 +2318,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -2512,10 +2334,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -2530,10 +2350,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>0</v>
@@ -2548,10 +2366,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -2566,10 +2382,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -2584,10 +2398,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -2602,10 +2414,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -2620,10 +2430,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2638,10 +2446,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2656,10 +2462,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -2696,10 +2500,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -2714,10 +2516,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.5725</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.133</v>
@@ -2732,10 +2532,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.015015</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.011503</v>
@@ -2750,10 +2548,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -2768,10 +2564,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.003512</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-0.001709</v>
@@ -2786,10 +2580,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.011503</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.009794000000000001</v>
@@ -2804,10 +2596,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2822,10 +2612,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.576012</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.134709</v>
@@ -2845,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3930,10 +3718,8 @@
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E36" s="5" t="n">
+        <v>0.0725</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0.061</v>
@@ -4029,10 +3815,8 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" s="5" t="n">
+        <v>0.015015</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>0.011503</v>
@@ -4062,10 +3846,8 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="5" t="n">
+        <v>0.011503</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>0.009794000000000001</v>
@@ -4192,6 +3974,1608 @@
       </c>
       <c r="G44" s="5" t="n">
         <v>2.8e-05</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cash Flows from Operating Activities</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>-0.643475</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>-0.296259</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Adjustments for non-cash items</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" s="5" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0.036791</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Adjustments for non-cash items</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Interest and accretion</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" s="5" t="n">
+        <v>0.037611</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.056733</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>-0.015193</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>-0.031268</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>-0.003345</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.008845</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.03828</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0.090449</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>-0.576012</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>-0.134709</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cash Flows from Financing Activities</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of common shares, net of share issuance costs</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cash Flows from Financing Activities</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cash Flows from Financing Activities</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Net decrease in cash</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>-0.003512</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>-0.001709</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bank and other charges</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" s="5" t="n">
+        <v>0.001149</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.000885</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.000541</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.000952</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Interest and accretion 11, 12</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>0.037611</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.056733</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.06512</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Listing fees</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>0.00997</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.007535</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.001847</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Management fees 15</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.112536</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.052286</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.14993</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0.009013</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0.018342</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.0105</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0.166293</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.037228</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.042962</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0.011308</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0.004234</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.009258000000000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Operating loss before other items</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>-0.606112</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>-0.297243</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-0.340158</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Gain on debt settlement 8, 10</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Gain (loss) on foreign exchange 12</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>-0.036791</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.002629</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Reversal of impairment</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.02088</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Write off inventory</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-0.003105</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Total other Items</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0.0009840000000000001</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>-2.057271</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss before income tax</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>-0.296259</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>-2.397429</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Income tax expense 16,18</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>-0.832062</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>-0.643475</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>-0.296259</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>-3.229491</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss is attributed to</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Shareholders of EGF Theramed Health Corp.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>-0.6230019999999999</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>-0.269253</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>-3.206161</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss is attributed to</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Non‐controlling interest 10</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.027006</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.02333</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss is attributed to</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Loss per share attributable to shareholders of the Company (basic and diluted)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>-2.8e-07</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss is attributed to</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares (basic and diluted)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>9.988878</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>11.211653</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>11.596277</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>g a Total</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0.02255</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>| Deficiency (2,478,779) (296,259) (2,703,038)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>-5.909979</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>-3.229491</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>6                                                                                                                     Shareholders’</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Non‐ Controlling Interest $ (1,335,881) — (27,006) (1,362,887) —</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>-1.386217</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>-0.02333</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>an</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>an of</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>an</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2023         loss 2024               loss 2025             Statements Ended  Canadian                                                 issued                             issued</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Investor communications</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>0.19728</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Loss on foreign exchange 12, 13</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-0.013275</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>-0.036791</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Reversal of impairment (Impairment of deposit and other) 5</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" s="5" t="n">
+        <v>-0.024088</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Other income 4</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.02088</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Total other items</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>-0.037363</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.0009840000000000001</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss is attributed to</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Non-controlling interest 10</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.020473</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.027006</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss is attributed to</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>(basic and diluted)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Note            Shares</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Balance, June 30, 2022 2,157,828 50,207,303 25,892 3,930,537 (55,183,628)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
+        <v>-2.335304</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>-1.315408</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Note            Shares</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Common shares issued for private placement 10 8,333,333 274,308 — 225,692 —</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Note            Shares</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Net loss for the year — — — — (623,002)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
+        <v>-0.643475</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>-0.020473</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Note            Shares</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Balance, June 30, 2023 10,491,161 50,481,611 25,892 4,156,229 (55,806,630)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" s="5" t="n">
+        <v>-2.478779</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-1.335881</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Note            Shares</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Common shares issued for exercise of warrants 10 900,000 96,375 — (24,375) —</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Note            Shares</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Net loss for the year — — — — (269,253)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" s="5" t="n">
+        <v>-0.296259</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-0.027006</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Note            Shares</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Balance, June 30, 2024 11,391,161 50,577,986 25,892 4,131,854 (56,075,883)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" s="5" t="n">
+        <v>-2.703038</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>-1.362887</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
